--- a/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_11.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1751026745_h_11.xlsx
@@ -658,7 +658,7 @@
         <v>0.008452553723509622</v>
       </c>
       <c r="C2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="K2" t="n">
-        <v>48185771</v>
+        <v>3985999</v>
       </c>
       <c r="L2" t="n">
-        <v>25154810</v>
+        <v>1681355</v>
       </c>
       <c r="M2" t="n">
-        <v>5901485</v>
+        <v>305607</v>
       </c>
       <c r="N2" t="n">
-        <v>273434</v>
+        <v>4385</v>
       </c>
       <c r="O2" t="n">
-        <v>3486790</v>
+        <v>163813</v>
       </c>
       <c r="P2" t="n">
-        <v>1295283</v>
+        <v>31975</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.999950110912323</v>
+        <v>0.9999179244041443</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8321331739425659</v>
+        <v>0.718742311000824</v>
       </c>
       <c r="S2" t="n">
-        <v>0.704581081867218</v>
+        <v>0.5276484489440918</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6311950087547302</v>
+        <v>0.3906024992465973</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2626745998859406</v>
+        <v>0.03827287629246712</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6767277121543884</v>
+        <v>0.4226537942886353</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8039583563804626</v>
+        <v>0.6120437383651733</v>
       </c>
       <c r="X2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>69810180</v>
+        <v>6346380</v>
       </c>
       <c r="AF2" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="AG2" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AH2" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AI2" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AK2" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9559435248374939</v>
+        <v>0.9546229243278503</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9116207361221313</v>
+        <v>0.912503182888031</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8580287098884583</v>
+        <v>0.8579802513122559</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615698337554932</v>
+        <v>0.6605058908462524</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.901967465877533</v>
+        <v>0.9019959568977356</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314546585083008</v>
+        <v>0.9314878582954407</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002025028638077513</v>
       </c>
       <c r="C3" t="n">
-        <v>575</v>
+        <v>163</v>
       </c>
       <c r="D3" t="n">
-        <v>48185771</v>
+        <v>3985999</v>
       </c>
       <c r="E3" t="n">
-        <v>6995315</v>
+        <v>954580</v>
       </c>
       <c r="F3" t="n">
-        <v>217160</v>
+        <v>41396</v>
       </c>
       <c r="G3" t="n">
-        <v>18233</v>
+        <v>2795</v>
       </c>
       <c r="H3" t="n">
-        <v>16600</v>
+        <v>3695</v>
       </c>
       <c r="I3" t="n">
-        <v>923</v>
+        <v>86</v>
       </c>
       <c r="J3" t="n">
-        <v>110762338</v>
+        <v>10069099</v>
       </c>
       <c r="K3" t="n">
-        <v>115420873</v>
+        <v>9867488</v>
       </c>
       <c r="L3" t="n">
-        <v>133735789</v>
+        <v>11570943</v>
       </c>
       <c r="M3" t="n">
-        <v>166817925</v>
+        <v>14994825</v>
       </c>
       <c r="N3" t="n">
-        <v>178823018</v>
+        <v>16215706</v>
       </c>
       <c r="O3" t="n">
-        <v>173296204</v>
+        <v>15679653</v>
       </c>
       <c r="P3" t="n">
-        <v>178131606</v>
+        <v>16201800</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8692367672920227</v>
+        <v>0.7990033030509949</v>
       </c>
       <c r="S3" t="n">
-        <v>0.693099319934845</v>
+        <v>0.5034138560295105</v>
       </c>
       <c r="T3" t="n">
-        <v>0.572411835193634</v>
+        <v>0.323604941368103</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2774697840213776</v>
+        <v>0.04866436496376991</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6210707426071167</v>
+        <v>0.3195864856243134</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6085297465324402</v>
+        <v>0.1648773849010468</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>53079081</v>
+        <v>4775969</v>
       </c>
       <c r="Z3" t="n">
-        <v>2185497</v>
+        <v>197364</v>
       </c>
       <c r="AA3" t="n">
-        <v>93996</v>
+        <v>8471</v>
       </c>
       <c r="AB3" t="n">
-        <v>75314</v>
+        <v>6869</v>
       </c>
       <c r="AC3" t="n">
-        <v>359</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>330</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>110765820</v>
+        <v>10069620</v>
       </c>
       <c r="AF3" t="n">
-        <v>122695174</v>
+        <v>11200265</v>
       </c>
       <c r="AG3" t="n">
-        <v>141081682</v>
+        <v>12784871</v>
       </c>
       <c r="AH3" t="n">
-        <v>168804129</v>
+        <v>15337760</v>
       </c>
       <c r="AI3" t="n">
-        <v>179257373</v>
+        <v>16295346</v>
       </c>
       <c r="AJ3" t="n">
-        <v>174411852</v>
+        <v>15853250</v>
       </c>
       <c r="AK3" t="n">
-        <v>178301599</v>
+        <v>16208790</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575085639953613</v>
+        <v>0.957354724407196</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097797274589539</v>
+        <v>0.9093555212020874</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570374250411987</v>
+        <v>0.8562913537025452</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6609038710594177</v>
+        <v>0.6595603227615356</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013426303863525</v>
+        <v>0.9008697271347046</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9311618804931641</v>
+        <v>0.9308778047561646</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03196808737360584</v>
       </c>
       <c r="C4" t="n">
-        <v>232</v>
+        <v>52</v>
       </c>
       <c r="D4" t="n">
-        <v>8959251</v>
+        <v>1393231</v>
       </c>
       <c r="E4" t="n">
-        <v>25154810</v>
+        <v>1681355</v>
       </c>
       <c r="F4" t="n">
-        <v>1835177</v>
+        <v>213425</v>
       </c>
       <c r="G4" t="n">
-        <v>110540</v>
+        <v>17289</v>
       </c>
       <c r="H4" t="n">
-        <v>215733</v>
+        <v>32671</v>
       </c>
       <c r="I4" t="n">
-        <v>17483</v>
+        <v>1883</v>
       </c>
       <c r="J4" t="n">
-        <v>3482</v>
+        <v>521</v>
       </c>
       <c r="K4" t="n">
-        <v>9720550</v>
+        <v>1559798</v>
       </c>
       <c r="L4" t="n">
-        <v>10546985</v>
+        <v>1505151</v>
       </c>
       <c r="M4" t="n">
-        <v>3448217</v>
+        <v>476792</v>
       </c>
       <c r="N4" t="n">
-        <v>767527</v>
+        <v>110187</v>
       </c>
       <c r="O4" t="n">
-        <v>1665637</v>
+        <v>223769</v>
       </c>
       <c r="P4" t="n">
-        <v>315849</v>
+        <v>20268</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999750256538391</v>
+        <v>0.9999589323997498</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8502803444862366</v>
+        <v>0.7567505836486816</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6987930536270142</v>
+        <v>0.5152463316917419</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6003679633140564</v>
+        <v>0.353961318731308</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2698695659637451</v>
+        <v>0.04284758120775223</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6477057933807373</v>
+        <v>0.363964170217514</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6927245259284973</v>
+        <v>0.2597745358943939</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2284621</v>
+        <v>212190</v>
       </c>
       <c r="Z4" t="n">
-        <v>33018842</v>
+        <v>3037162</v>
       </c>
       <c r="AA4" t="n">
-        <v>915390</v>
+        <v>83722</v>
       </c>
       <c r="AB4" t="n">
-        <v>61077</v>
+        <v>5633</v>
       </c>
       <c r="AC4" t="n">
-        <v>12548</v>
+        <v>1131</v>
       </c>
       <c r="AD4" t="n">
-        <v>748</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2446249</v>
+        <v>227021</v>
       </c>
       <c r="AG4" t="n">
-        <v>3201092</v>
+        <v>291223</v>
       </c>
       <c r="AH4" t="n">
-        <v>1462013</v>
+        <v>133857</v>
       </c>
       <c r="AI4" t="n">
-        <v>333172</v>
+        <v>30547</v>
       </c>
       <c r="AJ4" t="n">
-        <v>549989</v>
+        <v>50172</v>
       </c>
       <c r="AK4" t="n">
-        <v>145856</v>
+        <v>13278</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9567253589630127</v>
+        <v>0.9559868574142456</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106993675231934</v>
+        <v>0.9109266996383667</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8575327396392822</v>
+        <v>0.857134997844696</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612366437911987</v>
+        <v>0.6600327491760254</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016548991203308</v>
+        <v>0.9014324545860291</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313082695007324</v>
+        <v>0.9311826825141907</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>575</v>
+        <v>86</v>
       </c>
       <c r="D5" t="n">
-        <v>547898</v>
+        <v>123712</v>
       </c>
       <c r="E5" t="n">
-        <v>2848744</v>
+        <v>405362</v>
       </c>
       <c r="F5" t="n">
-        <v>5901485</v>
+        <v>305607</v>
       </c>
       <c r="G5" t="n">
-        <v>236333</v>
+        <v>27940</v>
       </c>
       <c r="H5" t="n">
-        <v>706700</v>
+        <v>75112</v>
       </c>
       <c r="I5" t="n">
-        <v>68123</v>
+        <v>6564</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7248806</v>
+        <v>1002715</v>
       </c>
       <c r="L5" t="n">
-        <v>11138416</v>
+        <v>1658551</v>
       </c>
       <c r="M5" t="n">
-        <v>4408373</v>
+        <v>638776</v>
       </c>
       <c r="N5" t="n">
-        <v>712021</v>
+        <v>85722</v>
       </c>
       <c r="O5" t="n">
-        <v>2127369</v>
+        <v>348765</v>
       </c>
       <c r="P5" t="n">
-        <v>833262</v>
+        <v>161957</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999806880950928</v>
+        <v>0.9999682903289795</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9060265421867371</v>
+        <v>0.843901515007019</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8799098134040833</v>
+        <v>0.8072793483734131</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9564915299415588</v>
+        <v>0.9320438504219055</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9918065071105957</v>
+        <v>0.9880659580230713</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9789949655532837</v>
+        <v>0.9651234149932861</v>
       </c>
       <c r="W5" t="n">
-        <v>0.993636429309845</v>
+        <v>0.9888995289802551</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>89118</v>
+        <v>8164</v>
       </c>
       <c r="Z5" t="n">
-        <v>946597</v>
+        <v>87570</v>
       </c>
       <c r="AA5" t="n">
-        <v>8835934</v>
+        <v>808667</v>
       </c>
       <c r="AB5" t="n">
-        <v>109931</v>
+        <v>10048</v>
       </c>
       <c r="AC5" t="n">
-        <v>321315</v>
+        <v>29301</v>
       </c>
       <c r="AD5" t="n">
-        <v>6963</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2355496</v>
+        <v>212745</v>
       </c>
       <c r="AG5" t="n">
-        <v>3274384</v>
+        <v>302744</v>
       </c>
       <c r="AH5" t="n">
-        <v>1473924</v>
+        <v>135716</v>
       </c>
       <c r="AI5" t="n">
-        <v>334164</v>
+        <v>30676</v>
       </c>
       <c r="AJ5" t="n">
-        <v>553878</v>
+        <v>50812</v>
       </c>
       <c r="AK5" t="n">
-        <v>146525</v>
+        <v>13405</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9734087586402893</v>
+        <v>0.9732111096382141</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9641398787498474</v>
+        <v>0.9638177752494812</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.983741283416748</v>
+        <v>0.983578622341156</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963043928146362</v>
+        <v>0.9962705373764038</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938869476318359</v>
+        <v>0.993848443031311</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983808398246765</v>
+        <v>0.9983745813369751</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>704</v>
+        <v>133</v>
       </c>
       <c r="D6" t="n">
-        <v>158097</v>
+        <v>22878</v>
       </c>
       <c r="E6" t="n">
-        <v>208727</v>
+        <v>28649</v>
       </c>
       <c r="F6" t="n">
-        <v>236801</v>
+        <v>25541</v>
       </c>
       <c r="G6" t="n">
-        <v>273434</v>
+        <v>4385</v>
       </c>
       <c r="H6" t="n">
-        <v>97391</v>
+        <v>7884</v>
       </c>
       <c r="I6" t="n">
-        <v>10301</v>
+        <v>637</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>71955</v>
+        <v>6631</v>
       </c>
       <c r="Z6" t="n">
-        <v>59191</v>
+        <v>5398</v>
       </c>
       <c r="AA6" t="n">
-        <v>120711</v>
+        <v>11132</v>
       </c>
       <c r="AB6" t="n">
-        <v>651291</v>
+        <v>59431</v>
       </c>
       <c r="AC6" t="n">
-        <v>77015</v>
+        <v>7033</v>
       </c>
       <c r="AD6" t="n">
-        <v>5292</v>
+        <v>482</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>771</v>
+        <v>44</v>
       </c>
       <c r="D7" t="n">
-        <v>52300</v>
+        <v>18517</v>
       </c>
       <c r="E7" t="n">
-        <v>448358</v>
+        <v>103248</v>
       </c>
       <c r="F7" t="n">
-        <v>1054736</v>
+        <v>166880</v>
       </c>
       <c r="G7" t="n">
-        <v>352185</v>
+        <v>48978</v>
       </c>
       <c r="H7" t="n">
-        <v>3486790</v>
+        <v>163813</v>
       </c>
       <c r="I7" t="n">
-        <v>219019</v>
+        <v>11098</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>247</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>8916</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>328269</v>
+        <v>30199</v>
       </c>
       <c r="AB7" t="n">
-        <v>83923</v>
+        <v>7730</v>
       </c>
       <c r="AC7" t="n">
-        <v>5060281</v>
+        <v>461766</v>
       </c>
       <c r="AD7" t="n">
-        <v>132523</v>
+        <v>12065</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>625</v>
+        <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>3004</v>
+        <v>1460</v>
       </c>
       <c r="E8" t="n">
-        <v>45841</v>
+        <v>13312</v>
       </c>
       <c r="F8" t="n">
-        <v>104343</v>
+        <v>29550</v>
       </c>
       <c r="G8" t="n">
-        <v>50236</v>
+        <v>13185</v>
       </c>
       <c r="H8" t="n">
-        <v>629213</v>
+        <v>104407</v>
       </c>
       <c r="I8" t="n">
-        <v>1295283</v>
+        <v>31975</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>308</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>891</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>3647</v>
+        <v>333</v>
       </c>
       <c r="AB8" t="n">
-        <v>2927</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>138752</v>
+        <v>12696</v>
       </c>
       <c r="AD8" t="n">
-        <v>1982020</v>
+        <v>180527</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
